--- a/task/可视化脚本_task1.xlsx
+++ b/task/可视化脚本_task1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victor/code/sql_transfer/sql_transfer/task/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victor/code/meetchances/solo-coder/sql_transfer/task/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B86734-A4CF-A84A-8175-731FB6E89548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F1A849-ACEB-5641-B0C3-3F5B12DFFBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="780" windowWidth="19420" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,20 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>可视化脚本</t>
   </si>
   <si>
     <t>24f864642c7643e9a9ccf94e4b6cd5d5</t>
-  </si>
-  <si>
-    <t>新指标脚本</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新指标ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>可视化脚本ID</t>
@@ -475,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="35.5" customWidth="1"/>
@@ -484,39 +476,29 @@
     <col min="4" max="4" width="41.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20" customHeight="1">
+    <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
     </row>
-    <row r="2" spans="1:4" ht="20" customHeight="1">
+    <row r="2" spans="1:2" ht="20" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" ht="20" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/task/可视化脚本_task1.xlsx
+++ b/task/可视化脚本_task1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victor/code/meetchances/solo-coder/sql_transfer/task/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F1A849-ACEB-5641-B0C3-3F5B12DFFBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB352E1B-65E9-D745-B628-9644E35B0552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="780" windowWidth="19420" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="780" windowWidth="31020" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>可视化脚本</t>
-  </si>
-  <si>
-    <t>24f864642c7643e9a9ccf94e4b6cd5d5</t>
   </si>
   <si>
     <t>可视化脚本ID</t>
@@ -38,13 +35,13 @@
 (
  SELECT sum(zc4ps_count)/sum(cyzcps_count) AS SBPC
  FROM YWYXJK_KACYZYSX
- where check_customs_code in ('5338','5304','5348','5316','5301','5345','5354','5320','5314','5317','5321')
+ where check_code in ('0001','0002','0003','0004','0005','0006')
   and i_e_flag='E' and check_state='M'
   and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 6)=to_char(sysdate(),'yyyymm')
 ), data_old AS (
  SELECT sum(zc4ps_count)/sum(cyzcps_count) AS SBPC
  FROM YWYXJK_KACYZYSX
- where check_customs_code in ('5338','5304','5348','5316','5301','5345','5354','5320','5314','5317','5321')
+ where check_code in ('0001','0002','0003','0004','0005','0006')
   and i_e_flag='E' and check_state='M'
   and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 8)&lt; TO_CHAR(ADD_MONTHS(sysdate(), -1), 'yyyyMMdd') 
  and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 8)&gt;= TO_CHAR(ADD_MONTHS(sysdate(), -1), 'yyyyMM') ||'01'
@@ -53,26 +50,23 @@
    ,CASE WHEN b.sbpc!=0 THEN abs(round((a.sbpc-b.sbpc)/b.sbpc*100,2)) ELSE 0 END                                 AS percen
        ,CASE WHEN b.sbpc!=0 AND (round((a.sbpc-b.sbpc)/b.sbpc*100,2) &gt; 15 or round((a.sbpc-b.sbpc)/b.sbpc*100,2) &lt; -15) THEN '1'  ELSE '0' END                                                                      AS status
        ,CASE WHEN b.sbpc!=0 AND round((a.sbpc-b.sbpc)/b.sbpc*100,2) &gt; 0 THEN '升'  ELSE '降' END AS literdecr
-       ,'查验正常4小时完成率'                                                                    AS label
+       ,'8小时完成率'                                                                    AS label
        ,'%'                                                                     AS cabinet
 FROM data_new a, data_old b</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2e28b07755b7469d92e4c4362b1b149d</t>
   </si>
   <si>
     <t>WITH data_new AS
 (
  SELECT sum(DCSX_DATE)/sum(CYPS_COUNT) AS SBPC
 FROM YWYXJK_KACYZYSX
- where check_customs_code in ('5338','5304','5348','5316','5301','5345','5354','5320','5314','5317','5321')
+ where check_code in ('0001','0002','0003','0004','0005','0006')
   and i_e_flag='E' and check_state='M'
   and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 6)=to_char(sysdate(),'yyyymm')
 ), data_old AS (
  SELECT  sum(DCSX_DATE)/sum(CYPS_COUNT) AS SBPC
 FROM YWYXJK_KACYZYSX
- where check_customs_code in ('5338','5304','5348','5316','5301','5345','5354','5320','5314','5317','5321')
+ where check_code in ('0001','0002','0003','0004','0005','0006')
   and i_e_flag='E' and check_state='M'
 and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 8)&lt; TO_CHAR(ADD_MONTHS(sysdate(), -1), 'yyyyMMdd') 
  and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 8)&gt;= TO_CHAR(ADD_MONTHS(sysdate(), -1), 'yyyyMM') ||'01'
@@ -81,7 +75,7 @@
    ,CASE WHEN b.sbpc!=0 THEN abs(round((a.sbpc-b.sbpc)/b.sbpc*100,2)) ELSE 0 END                                 AS percen
        ,CASE WHEN b.sbpc!=0 AND (round((a.sbpc-b.sbpc)/b.sbpc*100,2) &gt; 15 or round((a.sbpc-b.sbpc)/b.sbpc*100,2) &lt; -15) THEN '1'  ELSE '0' END                                                                      AS status
        ,CASE WHEN b.sbpc!=0 AND round((a.sbpc-b.sbpc)/b.sbpc*100,2) &gt; 0 THEN '升'  ELSE '降' END AS literdecr
-       ,'待查时长'                                                                    AS label
+       ,'时长'                                                                    AS label
        ,'小时'                                                                     AS cabinet
 FROM data_new a, data_old b</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -478,26 +472,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="20" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1">
+        <v>11111111111</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="20" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
+      <c r="A3" s="1">
+        <v>22222222222</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/task/可视化脚本_task1.xlsx
+++ b/task/可视化脚本_task1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victor/code/meetchances/solo-coder/sql_transfer/task/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB352E1B-65E9-D745-B628-9644E35B0552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A32AF20-798F-274E-BC95-590EC656EAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="780" windowWidth="31020" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,13 +34,13 @@
     <t>WITH data_new AS
 (
  SELECT sum(zc4ps_count)/sum(cyzcps_count) AS SBPC
- FROM YWYXJK_KACYZYSX
+ FROM UDWSDIUE
  where check_code in ('0001','0002','0003','0004','0005','0006')
   and i_e_flag='E' and check_state='M'
   and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 6)=to_char(sysdate(),'yyyymm')
 ), data_old AS (
  SELECT sum(zc4ps_count)/sum(cyzcps_count) AS SBPC
- FROM YWYXJK_KACYZYSX
+ FROM UDWSDIUE
  where check_code in ('0001','0002','0003','0004','0005','0006')
   and i_e_flag='E' and check_state='M'
   and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 8)&lt; TO_CHAR(ADD_MONTHS(sysdate(), -1), 'yyyyMMdd') 
@@ -59,13 +59,13 @@
     <t>WITH data_new AS
 (
  SELECT sum(DCSX_DATE)/sum(CYPS_COUNT) AS SBPC
-FROM YWYXJK_KACYZYSX
+FROM UDWSDIUE
  where check_code in ('0001','0002','0003','0004','0005','0006')
   and i_e_flag='E' and check_state='M'
   and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 6)=to_char(sysdate(),'yyyymm')
 ), data_old AS (
  SELECT  sum(DCSX_DATE)/sum(CYPS_COUNT) AS SBPC
-FROM YWYXJK_KACYZYSX
+FROM UDWSDIUE
  where check_code in ('0001','0002','0003','0004','0005','0006')
   and i_e_flag='E' and check_state='M'
 and SUBSTR(REPLACE(man_chk_time_end, '-', ''), 1, 8)&lt; TO_CHAR(ADD_MONTHS(sysdate(), -1), 'yyyyMMdd') 
